--- a/2023_zscore/zscore_2023_zori.xlsx
+++ b/2023_zscore/zscore_2023_zori.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C258"/>
+  <dimension ref="A1:D258"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,6 +367,11 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>zscore_raw</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>zscore</t>
         </is>
       </c>
@@ -381,6 +386,9 @@
       <c r="C2">
         <v>0.9719323113356957</v>
       </c>
+      <c r="D2">
+        <v>0.9719323113356957</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -392,6 +400,9 @@
       <c r="C3">
         <v>-0.2091647945943678</v>
       </c>
+      <c r="D3">
+        <v>-0.2091647945943678</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -403,6 +414,9 @@
       <c r="C4">
         <v>-0.2091647945943678</v>
       </c>
+      <c r="D4">
+        <v>-0.2091647945943678</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -414,6 +428,9 @@
       <c r="C5">
         <v>-0.2091647945943678</v>
       </c>
+      <c r="D5">
+        <v>-0.2091647945943678</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -425,6 +442,9 @@
       <c r="C6">
         <v>-0.2091647945943678</v>
       </c>
+      <c r="D6">
+        <v>-0.2091647945943678</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -436,6 +456,9 @@
       <c r="C7">
         <v>-0.2091647945943678</v>
       </c>
+      <c r="D7">
+        <v>-0.2091647945943678</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -447,6 +470,9 @@
       <c r="C8">
         <v>0.568506827124873</v>
       </c>
+      <c r="D8">
+        <v>0.568506827124873</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -458,6 +484,9 @@
       <c r="C9">
         <v>1.081042670716823</v>
       </c>
+      <c r="D9">
+        <v>1.081042670716823</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -469,6 +498,9 @@
       <c r="C10">
         <v>1.628030188256526</v>
       </c>
+      <c r="D10">
+        <v>1.628030188256526</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -480,6 +512,9 @@
       <c r="C11">
         <v>1.056745822057685</v>
       </c>
+      <c r="D11">
+        <v>1.056745822057685</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -491,6 +526,9 @@
       <c r="C12">
         <v>1.078611376770697</v>
       </c>
+      <c r="D12">
+        <v>1.078611376770697</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -502,6 +540,9 @@
       <c r="C13">
         <v>1.801627696129324</v>
       </c>
+      <c r="D13">
+        <v>1.801627696129324</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -513,6 +554,9 @@
       <c r="C14">
         <v>1.801627696129323</v>
       </c>
+      <c r="D14">
+        <v>1.801627696129323</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -524,6 +568,9 @@
       <c r="C15">
         <v>1.801627696129323</v>
       </c>
+      <c r="D15">
+        <v>1.801627696129323</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -535,6 +582,9 @@
       <c r="C16">
         <v>1.801627696129323</v>
       </c>
+      <c r="D16">
+        <v>1.801627696129323</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -546,6 +596,9 @@
       <c r="C17">
         <v>1.801627696129323</v>
       </c>
+      <c r="D17">
+        <v>1.801627696129323</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -557,6 +610,9 @@
       <c r="C18">
         <v>1.801627696129323</v>
       </c>
+      <c r="D18">
+        <v>1.801627696129323</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -568,6 +624,9 @@
       <c r="C19">
         <v>0.9719323113356957</v>
       </c>
+      <c r="D19">
+        <v>0.9719323113356957</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -579,6 +638,9 @@
       <c r="C20">
         <v>0.9719323113356957</v>
       </c>
+      <c r="D20">
+        <v>0.9719323113356957</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -590,6 +652,9 @@
       <c r="C21">
         <v>0.8747791253388179</v>
       </c>
+      <c r="D21">
+        <v>0.8747791253388179</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -601,6 +666,9 @@
       <c r="C22">
         <v>1.339423491280678</v>
       </c>
+      <c r="D22">
+        <v>1.339423491280678</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -612,6 +680,9 @@
       <c r="C23">
         <v>0.6844980667012147</v>
       </c>
+      <c r="D23">
+        <v>0.6844980667012147</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -623,6 +694,9 @@
       <c r="C24">
         <v>0.6844980667012147</v>
       </c>
+      <c r="D24">
+        <v>0.6844980667012147</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -634,6 +708,9 @@
       <c r="C25">
         <v>1.801627696129323</v>
       </c>
+      <c r="D25">
+        <v>1.801627696129323</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -645,6 +722,9 @@
       <c r="C26">
         <v>0.9719323113356957</v>
       </c>
+      <c r="D26">
+        <v>0.9719323113356957</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -656,6 +736,9 @@
       <c r="C27">
         <v>0.9719323113356957</v>
       </c>
+      <c r="D27">
+        <v>0.9719323113356957</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -667,6 +750,9 @@
       <c r="C28">
         <v>0.9504201710956649</v>
       </c>
+      <c r="D28">
+        <v>0.9504201710956649</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -678,6 +764,9 @@
       <c r="C29">
         <v>0.6844980667012147</v>
       </c>
+      <c r="D29">
+        <v>0.6844980667012147</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -689,6 +778,9 @@
       <c r="C30">
         <v>0.6844980667012147</v>
       </c>
+      <c r="D30">
+        <v>0.6844980667012147</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -700,6 +792,9 @@
       <c r="C31">
         <v>-2.856204671852369</v>
       </c>
+      <c r="D31">
+        <v>-2.856204671852369</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -711,6 +806,9 @@
       <c r="C32">
         <v>0.6844980667012147</v>
       </c>
+      <c r="D32">
+        <v>0.6844980667012147</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -722,6 +820,9 @@
       <c r="C33">
         <v>0.6844980667012147</v>
       </c>
+      <c r="D33">
+        <v>0.6844980667012147</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -733,6 +834,9 @@
       <c r="C34">
         <v>-3.610077542335251</v>
       </c>
+      <c r="D34">
+        <v>-3.610077542335251</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -744,6 +848,9 @@
       <c r="C35">
         <v>0.6844980667012147</v>
       </c>
+      <c r="D35">
+        <v>0.6844980667012147</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -755,6 +862,9 @@
       <c r="C36">
         <v>0.1043242590372187</v>
       </c>
+      <c r="D36">
+        <v>0.1043242590372187</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -766,6 +876,9 @@
       <c r="C37">
         <v>0.1043242590372187</v>
       </c>
+      <c r="D37">
+        <v>0.1043242590372187</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -777,6 +890,9 @@
       <c r="C38">
         <v>0.1043242590372187</v>
       </c>
+      <c r="D38">
+        <v>0.1043242590372187</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -788,6 +904,9 @@
       <c r="C39">
         <v>0.1043242590372187</v>
       </c>
+      <c r="D39">
+        <v>0.1043242590372187</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -799,6 +918,9 @@
       <c r="C40">
         <v>0.1043242590372187</v>
       </c>
+      <c r="D40">
+        <v>0.1043242590372187</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -810,6 +932,9 @@
       <c r="C41">
         <v>0.34892577814529</v>
       </c>
+      <c r="D41">
+        <v>0.34892577814529</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -821,6 +946,9 @@
       <c r="C42">
         <v>0.34892577814529</v>
       </c>
+      <c r="D42">
+        <v>0.34892577814529</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -832,6 +960,9 @@
       <c r="C43">
         <v>0.34892577814529</v>
       </c>
+      <c r="D43">
+        <v>0.34892577814529</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -843,6 +974,9 @@
       <c r="C44">
         <v>0.34892577814529</v>
       </c>
+      <c r="D44">
+        <v>0.34892577814529</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -854,6 +988,9 @@
       <c r="C45">
         <v>0.34892577814529</v>
       </c>
+      <c r="D45">
+        <v>0.34892577814529</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -865,6 +1002,9 @@
       <c r="C46">
         <v>0.34892577814529</v>
       </c>
+      <c r="D46">
+        <v>0.34892577814529</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -876,6 +1016,9 @@
       <c r="C47">
         <v>0.34892577814529</v>
       </c>
+      <c r="D47">
+        <v>0.34892577814529</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -887,6 +1030,9 @@
       <c r="C48">
         <v>0.3487437790410575</v>
       </c>
+      <c r="D48">
+        <v>0.3487437790410575</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -898,6 +1044,9 @@
       <c r="C49">
         <v>0.1258218128714769</v>
       </c>
+      <c r="D49">
+        <v>0.1258218128714769</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -909,6 +1058,9 @@
       <c r="C50">
         <v>0.1043242590372187</v>
       </c>
+      <c r="D50">
+        <v>0.1043242590372187</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -920,6 +1072,9 @@
       <c r="C51">
         <v>0.1043242590372187</v>
       </c>
+      <c r="D51">
+        <v>0.1043242590372187</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -931,6 +1086,9 @@
       <c r="C52">
         <v>0.1065027520997247</v>
       </c>
+      <c r="D52">
+        <v>0.1065027520997247</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -942,6 +1100,9 @@
       <c r="C53">
         <v>-4.104101435619761</v>
       </c>
+      <c r="D53">
+        <v>-4</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -953,6 +1114,9 @@
       <c r="C54">
         <v>-4.201208056412434</v>
       </c>
+      <c r="D54">
+        <v>-4</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -964,6 +1128,9 @@
       <c r="C55">
         <v>-3.512854187665196</v>
       </c>
+      <c r="D55">
+        <v>-3.512854187665196</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -975,6 +1142,9 @@
       <c r="C56">
         <v>0.2250341683774769</v>
       </c>
+      <c r="D56">
+        <v>0.2250341683774769</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -986,6 +1156,9 @@
       <c r="C57">
         <v>0.34892577814529</v>
       </c>
+      <c r="D57">
+        <v>0.34892577814529</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -997,6 +1170,9 @@
       <c r="C58">
         <v>0.34892577814529</v>
       </c>
+      <c r="D58">
+        <v>0.34892577814529</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -1008,6 +1184,9 @@
       <c r="C59">
         <v>0.2363335613724849</v>
       </c>
+      <c r="D59">
+        <v>0.2363335613724849</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -1019,6 +1198,9 @@
       <c r="C60">
         <v>0.375538866691117</v>
       </c>
+      <c r="D60">
+        <v>0.375538866691117</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -1030,6 +1212,9 @@
       <c r="C61">
         <v>0.05072103166869627</v>
       </c>
+      <c r="D61">
+        <v>0.05072103166869627</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -1041,6 +1226,9 @@
       <c r="C62">
         <v>-0.4066852134375866</v>
       </c>
+      <c r="D62">
+        <v>-0.4066852134375866</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -1052,6 +1240,9 @@
       <c r="C63">
         <v>-0.4105229350365596</v>
       </c>
+      <c r="D63">
+        <v>-0.4105229350365596</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -1063,6 +1254,9 @@
       <c r="C64">
         <v>0.4599993903197755</v>
       </c>
+      <c r="D64">
+        <v>0.4599993903197755</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -1074,6 +1268,9 @@
       <c r="C65">
         <v>0.4599993903197755</v>
       </c>
+      <c r="D65">
+        <v>0.4599993903197755</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -1085,6 +1282,9 @@
       <c r="C66">
         <v>0.4599993903197755</v>
       </c>
+      <c r="D66">
+        <v>0.4599993903197755</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -1096,6 +1296,9 @@
       <c r="C67">
         <v>0.4599993903197755</v>
       </c>
+      <c r="D67">
+        <v>0.4599993903197755</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -1107,6 +1310,9 @@
       <c r="C68">
         <v>0.4599993903197755</v>
       </c>
+      <c r="D68">
+        <v>0.4599993903197755</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -1118,6 +1324,9 @@
       <c r="C69">
         <v>0.3607738814509099</v>
       </c>
+      <c r="D69">
+        <v>0.3607738814509099</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -1129,6 +1338,9 @@
       <c r="C70">
         <v>0.4506566949112876</v>
       </c>
+      <c r="D70">
+        <v>0.4506566949112876</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -1140,6 +1352,9 @@
       <c r="C71">
         <v>-0.5471284696894041</v>
       </c>
+      <c r="D71">
+        <v>-0.5471284696894041</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -1151,6 +1366,9 @@
       <c r="C72">
         <v>-0.2091647945943678</v>
       </c>
+      <c r="D72">
+        <v>-0.2091647945943678</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -1162,6 +1380,9 @@
       <c r="C73">
         <v>-0.2091647945943678</v>
       </c>
+      <c r="D73">
+        <v>-0.2091647945943678</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -1173,6 +1394,9 @@
       <c r="C74">
         <v>-0.2091647945943678</v>
       </c>
+      <c r="D74">
+        <v>-0.2091647945943678</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -1184,6 +1408,9 @@
       <c r="C75">
         <v>-0.2091647945943678</v>
       </c>
+      <c r="D75">
+        <v>-0.2091647945943678</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -1195,6 +1422,9 @@
       <c r="C76">
         <v>-0.2091647945943678</v>
       </c>
+      <c r="D76">
+        <v>-0.2091647945943678</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -1206,6 +1436,9 @@
       <c r="C77">
         <v>-0.2091647945943678</v>
       </c>
+      <c r="D77">
+        <v>-0.2091647945943678</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -1217,6 +1450,9 @@
       <c r="C78">
         <v>0.765862263342718</v>
       </c>
+      <c r="D78">
+        <v>0.765862263342718</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -1228,6 +1464,9 @@
       <c r="C79">
         <v>0.765862263342718</v>
       </c>
+      <c r="D79">
+        <v>0.765862263342718</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -1239,6 +1478,9 @@
       <c r="C80">
         <v>0.765862263342718</v>
       </c>
+      <c r="D80">
+        <v>0.765862263342718</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -1250,6 +1492,9 @@
       <c r="C81">
         <v>0.765862263342718</v>
       </c>
+      <c r="D81">
+        <v>0.765862263342718</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -1261,6 +1506,9 @@
       <c r="C82">
         <v>0.04934493325826602</v>
       </c>
+      <c r="D82">
+        <v>0.04934493325826602</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -1272,6 +1520,9 @@
       <c r="C83">
         <v>-0.5397076636663645</v>
       </c>
+      <c r="D83">
+        <v>-0.5397076636663645</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -1283,6 +1534,9 @@
       <c r="C84">
         <v>-0.5397076636663645</v>
       </c>
+      <c r="D84">
+        <v>-0.5397076636663645</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -1294,6 +1548,9 @@
       <c r="C85">
         <v>-0.5397076636663645</v>
       </c>
+      <c r="D85">
+        <v>-0.5397076636663645</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -1305,6 +1562,9 @@
       <c r="C86">
         <v>0.5646744989794703</v>
       </c>
+      <c r="D86">
+        <v>0.5646744989794703</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -1316,6 +1576,9 @@
       <c r="C87">
         <v>0.765862263342718</v>
       </c>
+      <c r="D87">
+        <v>0.765862263342718</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -1327,6 +1590,9 @@
       <c r="C88">
         <v>0.755768572902197</v>
       </c>
+      <c r="D88">
+        <v>0.755768572902197</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -1338,6 +1604,9 @@
       <c r="C89">
         <v>-0.5397076636663645</v>
       </c>
+      <c r="D89">
+        <v>-0.5397076636663645</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -1349,6 +1618,9 @@
       <c r="C90">
         <v>-0.5397076636663645</v>
       </c>
+      <c r="D90">
+        <v>-0.5397076636663645</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -1360,6 +1632,9 @@
       <c r="C91">
         <v>-0.5397076636663645</v>
       </c>
+      <c r="D91">
+        <v>-0.5397076636663645</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -1371,6 +1646,9 @@
       <c r="C92">
         <v>-0.5467940091461632</v>
       </c>
+      <c r="D92">
+        <v>-0.5467940091461632</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -1382,6 +1660,9 @@
       <c r="C93">
         <v>0.7377186259623849</v>
       </c>
+      <c r="D93">
+        <v>0.7377186259623849</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -1393,6 +1674,9 @@
       <c r="C94">
         <v>-0.4450368995978037</v>
       </c>
+      <c r="D94">
+        <v>-0.4450368995978037</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -1404,6 +1688,9 @@
       <c r="C95">
         <v>-0.6623473346680163</v>
       </c>
+      <c r="D95">
+        <v>-0.6623473346680163</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -1415,6 +1702,9 @@
       <c r="C96">
         <v>-0.014326107038939</v>
       </c>
+      <c r="D96">
+        <v>-0.014326107038939</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -1426,6 +1716,9 @@
       <c r="C97">
         <v>-0.1738426359533586</v>
       </c>
+      <c r="D97">
+        <v>-0.1738426359533586</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -1437,6 +1730,9 @@
       <c r="C98">
         <v>1.732206545917031</v>
       </c>
+      <c r="D98">
+        <v>1.732206545917031</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -1448,6 +1744,9 @@
       <c r="C99">
         <v>1.789025068419533</v>
       </c>
+      <c r="D99">
+        <v>1.789025068419533</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -1459,6 +1758,9 @@
       <c r="C100">
         <v>-0.3463707335279288</v>
       </c>
+      <c r="D100">
+        <v>-0.3463707335279288</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -1470,6 +1772,9 @@
       <c r="C101">
         <v>-0.6623473346680163</v>
       </c>
+      <c r="D101">
+        <v>-0.6623473346680163</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -1481,6 +1786,9 @@
       <c r="C102">
         <v>-0.6623473346680163</v>
       </c>
+      <c r="D102">
+        <v>-0.6623473346680163</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -1492,6 +1800,9 @@
       <c r="C103">
         <v>-0.6623473346680163</v>
       </c>
+      <c r="D103">
+        <v>-0.6623473346680163</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -1503,6 +1814,9 @@
       <c r="C104">
         <v>-0.6623473346680163</v>
       </c>
+      <c r="D104">
+        <v>-0.6623473346680163</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -1514,6 +1828,9 @@
       <c r="C105">
         <v>-1.091109064482806</v>
       </c>
+      <c r="D105">
+        <v>-1.091109064482806</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -1525,6 +1842,9 @@
       <c r="C106">
         <v>-1.106598842546903</v>
       </c>
+      <c r="D106">
+        <v>-1.106598842546903</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -1536,6 +1856,9 @@
       <c r="C107">
         <v>-1.106598842546903</v>
       </c>
+      <c r="D107">
+        <v>-1.106598842546903</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -1547,6 +1870,9 @@
       <c r="C108">
         <v>-1.103731418519283</v>
       </c>
+      <c r="D108">
+        <v>-1.103731418519283</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -1558,6 +1884,9 @@
       <c r="C109">
         <v>-0.6623473346680163</v>
       </c>
+      <c r="D109">
+        <v>-0.6623473346680163</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -1569,6 +1898,9 @@
       <c r="C110">
         <v>-0.3463707335279288</v>
       </c>
+      <c r="D110">
+        <v>-0.3463707335279288</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -1580,6 +1912,9 @@
       <c r="C111">
         <v>-0.6623473346680163</v>
       </c>
+      <c r="D111">
+        <v>-0.6623473346680163</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -1591,6 +1926,9 @@
       <c r="C112">
         <v>-0.6623473346680163</v>
       </c>
+      <c r="D112">
+        <v>-0.6623473346680163</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -1602,6 +1940,9 @@
       <c r="C113">
         <v>-0.6827997047878432</v>
       </c>
+      <c r="D113">
+        <v>-0.6827997047878432</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -1613,6 +1954,9 @@
       <c r="C114">
         <v>-1.106598842546903</v>
       </c>
+      <c r="D114">
+        <v>-1.106598842546903</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -1624,6 +1968,9 @@
       <c r="C115">
         <v>-1.106598842546903</v>
       </c>
+      <c r="D115">
+        <v>-1.106598842546903</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -1635,6 +1982,9 @@
       <c r="C116">
         <v>-1.106598842546903</v>
       </c>
+      <c r="D116">
+        <v>-1.106598842546903</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -1646,6 +1996,9 @@
       <c r="C117">
         <v>-1.106598842546903</v>
       </c>
+      <c r="D117">
+        <v>-1.106598842546903</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -1657,6 +2010,9 @@
       <c r="C118">
         <v>-0.7237447741998754</v>
       </c>
+      <c r="D118">
+        <v>-0.7237447741998754</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -1668,6 +2024,9 @@
       <c r="C119">
         <v>-0.2901245366147584</v>
       </c>
+      <c r="D119">
+        <v>-0.2901245366147584</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -1679,6 +2038,9 @@
       <c r="C120">
         <v>-0.6310871129591855</v>
       </c>
+      <c r="D120">
+        <v>-0.6310871129591855</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -1690,6 +2052,9 @@
       <c r="C121">
         <v>-0.6623473346680163</v>
       </c>
+      <c r="D121">
+        <v>-0.6623473346680163</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -1701,6 +2066,9 @@
       <c r="C122">
         <v>-0.1604207516142576</v>
       </c>
+      <c r="D122">
+        <v>-0.1604207516142576</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -1712,6 +2080,9 @@
       <c r="C123">
         <v>-0.04261413049171166</v>
       </c>
+      <c r="D123">
+        <v>-0.04261413049171166</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -1723,6 +2094,9 @@
       <c r="C124">
         <v>-0.04261413049171166</v>
       </c>
+      <c r="D124">
+        <v>-0.04261413049171166</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -1734,6 +2108,9 @@
       <c r="C125">
         <v>-0.03413132592229449</v>
       </c>
+      <c r="D125">
+        <v>-0.03413132592229449</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -1745,6 +2122,9 @@
       <c r="C126">
         <v>-0.04261413049171166</v>
       </c>
+      <c r="D126">
+        <v>-0.04261413049171166</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -1756,6 +2136,9 @@
       <c r="C127">
         <v>0.1183338531041961</v>
       </c>
+      <c r="D127">
+        <v>0.1183338531041961</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -1767,6 +2150,9 @@
       <c r="C128">
         <v>-0.459811756968235</v>
       </c>
+      <c r="D128">
+        <v>-0.459811756968235</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -1778,6 +2164,9 @@
       <c r="C129">
         <v>-0.2976646851975769</v>
       </c>
+      <c r="D129">
+        <v>-0.2976646851975769</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -1789,6 +2178,9 @@
       <c r="C130">
         <v>0.4599993903197755</v>
       </c>
+      <c r="D130">
+        <v>0.4599993903197755</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -1800,6 +2192,9 @@
       <c r="C131">
         <v>-0.970582056365131</v>
       </c>
+      <c r="D131">
+        <v>-0.970582056365131</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -1811,6 +2206,9 @@
       <c r="C132">
         <v>-0.970582056365131</v>
       </c>
+      <c r="D132">
+        <v>-0.970582056365131</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -1822,6 +2220,9 @@
       <c r="C133">
         <v>-0.970582056365131</v>
       </c>
+      <c r="D133">
+        <v>-0.970582056365131</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -1833,6 +2234,9 @@
       <c r="C134">
         <v>-0.6560856875440059</v>
       </c>
+      <c r="D134">
+        <v>-0.6560856875440059</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -1844,6 +2248,9 @@
       <c r="C135">
         <v>0.4599993903197755</v>
       </c>
+      <c r="D135">
+        <v>0.4599993903197755</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -1855,6 +2262,9 @@
       <c r="C136">
         <v>-0.2223016535673761</v>
       </c>
+      <c r="D136">
+        <v>-0.2223016535673761</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -1866,6 +2276,9 @@
       <c r="C137">
         <v>-0.459811756968235</v>
       </c>
+      <c r="D137">
+        <v>-0.459811756968235</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -1877,6 +2290,9 @@
       <c r="C138">
         <v>-0.2716450850033596</v>
       </c>
+      <c r="D138">
+        <v>-0.2716450850033596</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -1888,6 +2304,9 @@
       <c r="C139">
         <v>0.06779142734119536</v>
       </c>
+      <c r="D139">
+        <v>0.06779142734119536</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -1899,6 +2318,9 @@
       <c r="C140">
         <v>0.2687340447120913</v>
       </c>
+      <c r="D140">
+        <v>0.2687340447120913</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -1910,6 +2332,9 @@
       <c r="C141">
         <v>-0.970582056365131</v>
       </c>
+      <c r="D141">
+        <v>-0.970582056365131</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -1921,6 +2346,9 @@
       <c r="C142">
         <v>-0.970582056365131</v>
       </c>
+      <c r="D142">
+        <v>-0.970582056365131</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -1932,6 +2360,9 @@
       <c r="C143">
         <v>-0.970582056365131</v>
       </c>
+      <c r="D143">
+        <v>-0.970582056365131</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -1943,6 +2374,9 @@
       <c r="C144">
         <v>-0.9652002582913346</v>
       </c>
+      <c r="D144">
+        <v>-0.9652002582913346</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -1954,6 +2388,9 @@
       <c r="C145">
         <v>-0.8050197882332532</v>
       </c>
+      <c r="D145">
+        <v>-0.8050197882332532</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -1965,6 +2402,9 @@
       <c r="C146">
         <v>-0.8513474915141523</v>
       </c>
+      <c r="D146">
+        <v>-0.8513474915141523</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -1976,6 +2416,9 @@
       <c r="C147">
         <v>-0.8130731079122555</v>
       </c>
+      <c r="D147">
+        <v>-0.8130731079122555</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -1987,6 +2430,9 @@
       <c r="C148">
         <v>-0.4152851042914598</v>
       </c>
+      <c r="D148">
+        <v>-0.4152851042914598</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -1998,6 +2444,9 @@
       <c r="C149">
         <v>0.1875174410479998</v>
       </c>
+      <c r="D149">
+        <v>0.1875174410479998</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -2009,6 +2458,9 @@
       <c r="C150">
         <v>0.1875174410479998</v>
       </c>
+      <c r="D150">
+        <v>0.1875174410479998</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -2020,6 +2472,9 @@
       <c r="C151">
         <v>-0.04530902774889038</v>
       </c>
+      <c r="D151">
+        <v>-0.04530902774889038</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -2031,6 +2486,9 @@
       <c r="C152">
         <v>1.336665060966025</v>
       </c>
+      <c r="D152">
+        <v>1.336665060966025</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -2042,6 +2500,9 @@
       <c r="C153">
         <v>0.871524131168492</v>
       </c>
+      <c r="D153">
+        <v>0.871524131168492</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -2053,6 +2514,9 @@
       <c r="C154">
         <v>-0.08115781954685297</v>
       </c>
+      <c r="D154">
+        <v>-0.08115781954685297</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -2064,6 +2528,9 @@
       <c r="C155">
         <v>-0.793540216007574</v>
       </c>
+      <c r="D155">
+        <v>-0.793540216007574</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -2075,6 +2542,9 @@
       <c r="C156">
         <v>-0.793540216007574</v>
       </c>
+      <c r="D156">
+        <v>-0.793540216007574</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -2086,6 +2556,9 @@
       <c r="C157">
         <v>-0.793540216007574</v>
       </c>
+      <c r="D157">
+        <v>-0.793540216007574</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -2097,6 +2570,9 @@
       <c r="C158">
         <v>-0.793540216007574</v>
       </c>
+      <c r="D158">
+        <v>-0.793540216007574</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159">
@@ -2108,6 +2584,9 @@
       <c r="C159">
         <v>-0.793540216007574</v>
       </c>
+      <c r="D159">
+        <v>-0.793540216007574</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -2119,6 +2598,9 @@
       <c r="C160">
         <v>-0.793540216007574</v>
       </c>
+      <c r="D160">
+        <v>-0.793540216007574</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -2130,6 +2612,9 @@
       <c r="C161">
         <v>-0.8105452493123971</v>
       </c>
+      <c r="D161">
+        <v>-0.8105452493123971</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -2141,6 +2626,9 @@
       <c r="C162">
         <v>-0.8017225352848479</v>
       </c>
+      <c r="D162">
+        <v>-0.8017225352848479</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -2152,6 +2640,9 @@
       <c r="C163">
         <v>-0.5260791503314495</v>
       </c>
+      <c r="D163">
+        <v>-0.5260791503314495</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -2163,6 +2654,9 @@
       <c r="C164">
         <v>-0.7082295930246049</v>
       </c>
+      <c r="D164">
+        <v>-0.7082295930246049</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -2174,6 +2668,9 @@
       <c r="C165">
         <v>-0.5017201054485739</v>
       </c>
+      <c r="D165">
+        <v>-0.5017201054485739</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -2185,6 +2682,9 @@
       <c r="C166">
         <v>-0.09170822565414424</v>
       </c>
+      <c r="D166">
+        <v>-0.09170822565414424</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -2196,6 +2696,9 @@
       <c r="C167">
         <v>0.6124052965882286</v>
       </c>
+      <c r="D167">
+        <v>0.6124052965882286</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -2207,6 +2710,9 @@
       <c r="C168">
         <v>-0.4448050316482888</v>
       </c>
+      <c r="D168">
+        <v>-0.4448050316482888</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -2218,6 +2724,9 @@
       <c r="C169">
         <v>-1.207593191616505</v>
       </c>
+      <c r="D169">
+        <v>-1.207593191616505</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -2229,6 +2738,9 @@
       <c r="C170">
         <v>-0.07234136289155788</v>
       </c>
+      <c r="D170">
+        <v>-0.07234136289155788</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -2240,6 +2752,9 @@
       <c r="C171">
         <v>-0.07234136289155788</v>
       </c>
+      <c r="D171">
+        <v>-0.07234136289155788</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -2251,6 +2766,9 @@
       <c r="C172">
         <v>-0.07234136289155788</v>
       </c>
+      <c r="D172">
+        <v>-0.07234136289155788</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -2262,6 +2780,9 @@
       <c r="C173">
         <v>-0.07234136289155788</v>
       </c>
+      <c r="D173">
+        <v>-0.07234136289155788</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -2273,6 +2794,9 @@
       <c r="C174">
         <v>-0.07234136289155788</v>
       </c>
+      <c r="D174">
+        <v>-0.07234136289155788</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -2284,6 +2808,9 @@
       <c r="C175">
         <v>-0.07234136289155788</v>
       </c>
+      <c r="D175">
+        <v>-0.07234136289155788</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -2295,6 +2822,9 @@
       <c r="C176">
         <v>-0.07234136289155788</v>
       </c>
+      <c r="D176">
+        <v>-0.07234136289155788</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -2306,6 +2836,9 @@
       <c r="C177">
         <v>-2.821211074801498</v>
       </c>
+      <c r="D177">
+        <v>-2.821211074801498</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -2317,6 +2850,9 @@
       <c r="C178">
         <v>-3.498611184000688</v>
       </c>
+      <c r="D178">
+        <v>-3.498611184000688</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -2328,6 +2864,9 @@
       <c r="C179">
         <v>0.6196875548491445</v>
       </c>
+      <c r="D179">
+        <v>0.6196875548491445</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -2339,6 +2878,9 @@
       <c r="C180">
         <v>-0.970582056365131</v>
       </c>
+      <c r="D180">
+        <v>-0.970582056365131</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -2350,6 +2892,9 @@
       <c r="C181">
         <v>-0.970582056365131</v>
       </c>
+      <c r="D181">
+        <v>-0.970582056365131</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -2361,6 +2906,9 @@
       <c r="C182">
         <v>-0.5583977252900033</v>
       </c>
+      <c r="D182">
+        <v>-0.5583977252900033</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -2372,6 +2920,9 @@
       <c r="C183">
         <v>-0.5397076636663645</v>
       </c>
+      <c r="D183">
+        <v>-0.5397076636663645</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -2383,6 +2934,9 @@
       <c r="C184">
         <v>-1.263520721869985</v>
       </c>
+      <c r="D184">
+        <v>-1.263520721869985</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -2394,6 +2948,9 @@
       <c r="C185">
         <v>-1.247861849748935</v>
       </c>
+      <c r="D185">
+        <v>-1.247861849748935</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -2405,6 +2962,9 @@
       <c r="C186">
         <v>1.07231352316838</v>
       </c>
+      <c r="D186">
+        <v>1.07231352316838</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187">
@@ -2416,6 +2976,9 @@
       <c r="C187">
         <v>0.765862263342718</v>
       </c>
+      <c r="D187">
+        <v>0.765862263342718</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -2427,6 +2990,9 @@
       <c r="C188">
         <v>1.078611376770697</v>
       </c>
+      <c r="D188">
+        <v>1.078611376770697</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -2438,6 +3004,9 @@
       <c r="C189">
         <v>0.765862263342718</v>
       </c>
+      <c r="D189">
+        <v>0.765862263342718</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -2449,6 +3018,9 @@
       <c r="C190">
         <v>0.7713410836984739</v>
       </c>
+      <c r="D190">
+        <v>0.7713410836984739</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -2460,6 +3032,9 @@
       <c r="C191">
         <v>1.078611376770697</v>
       </c>
+      <c r="D191">
+        <v>1.078611376770697</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192">
@@ -2471,6 +3046,9 @@
       <c r="C192">
         <v>1.051296153293246</v>
       </c>
+      <c r="D192">
+        <v>1.051296153293246</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -2482,6 +3060,9 @@
       <c r="C193">
         <v>-1.263520721869985</v>
       </c>
+      <c r="D193">
+        <v>-1.263520721869985</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -2493,6 +3074,9 @@
       <c r="C194">
         <v>-1.263520721869984</v>
       </c>
+      <c r="D194">
+        <v>-1.263520721869984</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -2504,6 +3088,9 @@
       <c r="C195">
         <v>-1.263520721869985</v>
       </c>
+      <c r="D195">
+        <v>-1.263520721869985</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -2515,6 +3102,9 @@
       <c r="C196">
         <v>-1.263520721869985</v>
       </c>
+      <c r="D196">
+        <v>-1.263520721869985</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -2526,6 +3116,9 @@
       <c r="C197">
         <v>-1.122327299726414</v>
       </c>
+      <c r="D197">
+        <v>-1.122327299726414</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -2537,6 +3130,9 @@
       <c r="C198">
         <v>-1.263520721869985</v>
       </c>
+      <c r="D198">
+        <v>-1.263520721869985</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -2548,6 +3144,9 @@
       <c r="C199">
         <v>-1.26275514099029</v>
       </c>
+      <c r="D199">
+        <v>-1.26275514099029</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -2559,6 +3158,9 @@
       <c r="C200">
         <v>-1.247274263828754</v>
       </c>
+      <c r="D200">
+        <v>-1.247274263828754</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -2570,6 +3172,9 @@
       <c r="C201">
         <v>-1.263520721869985</v>
       </c>
+      <c r="D201">
+        <v>-1.263520721869985</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -2581,6 +3186,9 @@
       <c r="C202">
         <v>1.622084403899201</v>
       </c>
+      <c r="D202">
+        <v>1.622084403899201</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -2592,6 +3200,9 @@
       <c r="C203">
         <v>0.2446005639997169</v>
       </c>
+      <c r="D203">
+        <v>0.2446005639997169</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -2603,6 +3214,9 @@
       <c r="C204">
         <v>1.389028734381662</v>
       </c>
+      <c r="D204">
+        <v>1.389028734381662</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -2614,6 +3228,9 @@
       <c r="C205">
         <v>1.628030188256526</v>
       </c>
+      <c r="D205">
+        <v>1.628030188256526</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -2625,6 +3242,9 @@
       <c r="C206">
         <v>0.6175225251791912</v>
       </c>
+      <c r="D206">
+        <v>0.6175225251791912</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207">
@@ -2636,6 +3256,9 @@
       <c r="C207">
         <v>-0.04158302608923863</v>
       </c>
+      <c r="D207">
+        <v>-0.04158302608923863</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208">
@@ -2647,6 +3270,9 @@
       <c r="C208">
         <v>0.6196875548491445</v>
       </c>
+      <c r="D208">
+        <v>0.6196875548491445</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209">
@@ -2658,6 +3284,9 @@
       <c r="C209">
         <v>-0.07711163839094387</v>
       </c>
+      <c r="D209">
+        <v>-0.07711163839094387</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210">
@@ -2669,6 +3298,9 @@
       <c r="C210">
         <v>0.6196875548491445</v>
       </c>
+      <c r="D210">
+        <v>0.6196875548491445</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211">
@@ -2680,6 +3312,9 @@
       <c r="C211">
         <v>0.6196875548491445</v>
       </c>
+      <c r="D211">
+        <v>0.6196875548491445</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212">
@@ -2691,6 +3326,9 @@
       <c r="C212">
         <v>0.6196875548491461</v>
       </c>
+      <c r="D212">
+        <v>0.6196875548491461</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213">
@@ -2702,6 +3340,9 @@
       <c r="C213">
         <v>1.182239424336855</v>
       </c>
+      <c r="D213">
+        <v>1.182239424336855</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214">
@@ -2713,6 +3354,9 @@
       <c r="C214">
         <v>1.182239424336855</v>
       </c>
+      <c r="D214">
+        <v>1.182239424336855</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215">
@@ -2724,6 +3368,9 @@
       <c r="C215">
         <v>1.160891318098464</v>
       </c>
+      <c r="D215">
+        <v>1.160891318098464</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216">
@@ -2735,6 +3382,9 @@
       <c r="C216">
         <v>-1.187441220482092</v>
       </c>
+      <c r="D216">
+        <v>-1.187441220482092</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217">
@@ -2746,6 +3396,9 @@
       <c r="C217">
         <v>1.129313630394315</v>
       </c>
+      <c r="D217">
+        <v>1.129313630394315</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218">
@@ -2757,6 +3410,9 @@
       <c r="C218">
         <v>-0.1522587060302808</v>
       </c>
+      <c r="D218">
+        <v>-0.1522587060302808</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219">
@@ -2768,6 +3424,9 @@
       <c r="C219">
         <v>1.197918042597858</v>
       </c>
+      <c r="D219">
+        <v>1.197918042597858</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220">
@@ -2779,6 +3438,9 @@
       <c r="C220">
         <v>-0.07234136289155788</v>
       </c>
+      <c r="D220">
+        <v>-0.07234136289155788</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221">
@@ -2790,6 +3452,9 @@
       <c r="C221">
         <v>0.973519608183488</v>
       </c>
+      <c r="D221">
+        <v>0.973519608183488</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222">
@@ -2801,6 +3466,9 @@
       <c r="C222">
         <v>-0.1536478582150196</v>
       </c>
+      <c r="D222">
+        <v>-0.1536478582150196</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223">
@@ -2812,6 +3480,9 @@
       <c r="C223">
         <v>-0.1536478582150196</v>
       </c>
+      <c r="D223">
+        <v>-0.1536478582150196</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224">
@@ -2823,6 +3494,9 @@
       <c r="C224">
         <v>0.2611223182340292</v>
       </c>
+      <c r="D224">
+        <v>0.2611223182340292</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225">
@@ -2834,6 +3508,9 @@
       <c r="C225">
         <v>0.5377900542980403</v>
       </c>
+      <c r="D225">
+        <v>0.5377900542980403</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226">
@@ -2845,6 +3522,9 @@
       <c r="C226">
         <v>-0.1536478582150196</v>
       </c>
+      <c r="D226">
+        <v>-0.1536478582150196</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227">
@@ -2856,6 +3536,9 @@
       <c r="C227">
         <v>0.4020411147429799</v>
       </c>
+      <c r="D227">
+        <v>0.4020411147429799</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228">
@@ -2867,6 +3550,9 @@
       <c r="C228">
         <v>1.197918042597859</v>
       </c>
+      <c r="D228">
+        <v>1.197918042597859</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229">
@@ -2878,6 +3564,9 @@
       <c r="C229">
         <v>0.3779420515996722</v>
       </c>
+      <c r="D229">
+        <v>0.3779420515996722</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230">
@@ -2889,6 +3578,9 @@
       <c r="C230">
         <v>-0.1536478582150196</v>
       </c>
+      <c r="D230">
+        <v>-0.1536478582150196</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231">
@@ -2900,6 +3592,9 @@
       <c r="C231">
         <v>-0.1536478582150196</v>
       </c>
+      <c r="D231">
+        <v>-0.1536478582150196</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232">
@@ -2911,6 +3606,9 @@
       <c r="C232">
         <v>0.6498170102924241</v>
       </c>
+      <c r="D232">
+        <v>0.6498170102924241</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233">
@@ -2922,6 +3620,9 @@
       <c r="C233">
         <v>0.9363897296944924</v>
       </c>
+      <c r="D233">
+        <v>0.9363897296944924</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234">
@@ -2933,6 +3634,9 @@
       <c r="C234">
         <v>-0.1536478582150196</v>
       </c>
+      <c r="D234">
+        <v>-0.1536478582150196</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235">
@@ -2944,6 +3648,9 @@
       <c r="C235">
         <v>-0.1536478582150196</v>
       </c>
+      <c r="D235">
+        <v>-0.1536478582150196</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236">
@@ -2955,6 +3662,9 @@
       <c r="C236">
         <v>0.3807598137768599</v>
       </c>
+      <c r="D236">
+        <v>0.3807598137768599</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237">
@@ -2966,6 +3676,9 @@
       <c r="C237">
         <v>-0.1440190943768257</v>
       </c>
+      <c r="D237">
+        <v>-0.1440190943768257</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238">
@@ -2977,6 +3690,9 @@
       <c r="C238">
         <v>1.182239424336855</v>
       </c>
+      <c r="D238">
+        <v>1.182239424336855</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239">
@@ -2988,6 +3704,9 @@
       <c r="C239">
         <v>0.3497589562276368</v>
       </c>
+      <c r="D239">
+        <v>0.3497589562276368</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240">
@@ -2999,6 +3718,9 @@
       <c r="C240">
         <v>0.9860912973223056</v>
       </c>
+      <c r="D240">
+        <v>0.9860912973223056</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241">
@@ -3010,6 +3732,9 @@
       <c r="C241">
         <v>1.614872635838665</v>
       </c>
+      <c r="D241">
+        <v>1.614872635838665</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242">
@@ -3021,6 +3746,9 @@
       <c r="C242">
         <v>1.628030188256526</v>
       </c>
+      <c r="D242">
+        <v>1.628030188256526</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243">
@@ -3032,6 +3760,9 @@
       <c r="C243">
         <v>1.628030188256526</v>
       </c>
+      <c r="D243">
+        <v>1.628030188256526</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244">
@@ -3043,6 +3774,9 @@
       <c r="C244">
         <v>1.197918042597859</v>
       </c>
+      <c r="D244">
+        <v>1.197918042597859</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245">
@@ -3054,6 +3788,9 @@
       <c r="C245">
         <v>1.628030188256526</v>
       </c>
+      <c r="D245">
+        <v>1.628030188256526</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246">
@@ -3065,6 +3802,9 @@
       <c r="C246">
         <v>1.201096175385651</v>
       </c>
+      <c r="D246">
+        <v>1.201096175385651</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247">
@@ -3076,6 +3816,9 @@
       <c r="C247">
         <v>1.197918042597859</v>
       </c>
+      <c r="D247">
+        <v>1.197918042597859</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248">
@@ -3087,6 +3830,9 @@
       <c r="C248">
         <v>1.197918042597859</v>
       </c>
+      <c r="D248">
+        <v>1.197918042597859</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249">
@@ -3098,6 +3844,9 @@
       <c r="C249">
         <v>1.197918042597859</v>
       </c>
+      <c r="D249">
+        <v>1.197918042597859</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250">
@@ -3109,6 +3858,9 @@
       <c r="C250">
         <v>-0.459811756968235</v>
       </c>
+      <c r="D250">
+        <v>-0.459811756968235</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251">
@@ -3120,6 +3872,9 @@
       <c r="C251">
         <v>-0.5397076636663645</v>
       </c>
+      <c r="D251">
+        <v>-0.5397076636663645</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252">
@@ -3131,6 +3886,9 @@
       <c r="C252">
         <v>-0.5382942703295354</v>
       </c>
+      <c r="D252">
+        <v>-0.5382942703295354</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253">
@@ -3142,6 +3900,9 @@
       <c r="C253">
         <v>-1.106598842546903</v>
       </c>
+      <c r="D253">
+        <v>-1.106598842546903</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254">
@@ -3153,6 +3914,9 @@
       <c r="C254">
         <v>-0.04261413049171166</v>
       </c>
+      <c r="D254">
+        <v>-0.04261413049171166</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255">
@@ -3164,6 +3928,9 @@
       <c r="C255">
         <v>0.2020215552947479</v>
       </c>
+      <c r="D255">
+        <v>0.2020215552947479</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256">
@@ -3175,6 +3942,9 @@
       <c r="C256">
         <v>0.1875174410479998</v>
       </c>
+      <c r="D256">
+        <v>0.1875174410479998</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257">
@@ -3186,6 +3956,9 @@
       <c r="C257">
         <v>-1.13302461671711</v>
       </c>
+      <c r="D257">
+        <v>-1.13302461671711</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258">
@@ -3195,6 +3968,9 @@
         <v>1606.232129600616</v>
       </c>
       <c r="C258">
+        <v>1.215600726488291</v>
+      </c>
+      <c r="D258">
         <v>1.215600726488291</v>
       </c>
     </row>
